--- a/src/test/resources/API_dataSheet.xlsx
+++ b/src/test/resources/API_dataSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="creation" sheetId="1" r:id="rId1"/>
@@ -20,21 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
   <si>
-    <t>Pasword98901jkdfs01</t>
+    <t>TestName5243jdfh04</t>
   </si>
   <si>
-    <t>testemailmvb855nvj04@email.com01</t>
+    <t>testemailmvb855nvj04@email.com04</t>
   </si>
   <si>
-    <t>TestName5243jdfh03</t>
-  </si>
-  <si>
-    <t>testemailmvb855nvj04@email.com03</t>
-  </si>
-  <si>
-    <t>Pasword98901jkdfs0894</t>
+    <t>Pasword98901jkdfs0895</t>
   </si>
 </sst>
 </file>
@@ -373,21 +367,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
       <c r="D1">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B1" r:id="rId1"/>
+    <hyperlink ref="B1" r:id="rId1" display="testemailmvb855nvj04@email.com03"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -399,7 +393,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -407,12 +401,12 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1"/>
+    <hyperlink ref="A1" r:id="rId1" display="testemailmvb855nvj04@email.com03"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/API_dataSheet.xlsx
+++ b/src/test/resources/API_dataSheet.xlsx
@@ -22,13 +22,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
   <si>
-    <t>TestName5243jdfh04</t>
+    <t>TestName5243jdfh22</t>
   </si>
   <si>
-    <t>testemailmvb855nvj04@email.com04</t>
+    <t>testemailmvb855nvj04@email.com22</t>
   </si>
   <si>
-    <t>Pasword98901jkdfs0895</t>
+    <t>Pasword98901jkdfs0913</t>
   </si>
 </sst>
 </file>
@@ -376,7 +376,7 @@
         <v>2</v>
       </c>
       <c r="D1">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
